--- a/data/hardtail/Enigma Explor 2025.xlsx
+++ b/data/hardtail/Enigma Explor 2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/hardtail/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3F772B8-9149-6147-8D59-C1502331319C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96A98F2B-D508-A947-84CA-9C825522F982}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2520" yWindow="740" windowWidth="25860" windowHeight="16640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="109">
   <si>
     <t>brand</t>
   </si>
@@ -329,9 +329,6 @@
     <t>no</t>
   </si>
   <si>
-    <t>a8:f33</t>
-  </si>
-  <si>
     <t>estimated axle crown 493.75</t>
   </si>
   <si>
@@ -339,6 +336,30 @@
   </si>
   <si>
     <t>120 mm w 25% sag</t>
+  </si>
+  <si>
+    <t>class</t>
+  </si>
+  <si>
+    <t>hardtail</t>
+  </si>
+  <si>
+    <t>handlebar</t>
+  </si>
+  <si>
+    <t>fork</t>
+  </si>
+  <si>
+    <t>suspension</t>
+  </si>
+  <si>
+    <t>flat bar</t>
+  </si>
+  <si>
+    <t>frame_weight</t>
+  </si>
+  <si>
+    <t>a8:f34</t>
   </si>
 </sst>
 </file>
@@ -677,7 +698,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H70"/>
+  <dimension ref="A1:H74"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -728,7 +749,7 @@
         <v>10</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="C7" t="s">
         <v>19</v>
@@ -1015,325 +1036,354 @@
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>44</v>
+      <c r="A22" s="1" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>45</v>
-      </c>
-      <c r="G23" s="1" t="s">
-        <v>99</v>
+        <v>44</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
+        <v>45</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
         <v>46</v>
       </c>
-      <c r="G24" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="H24">
+      <c r="G25" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="H25">
         <f>501-0.25*100</f>
         <v>476</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
         <v>47</v>
       </c>
-      <c r="G25" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="H25">
+      <c r="G26" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="H26">
         <f>521-0.25*120</f>
         <v>491</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>48</v>
-      </c>
-    </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>51</v>
-      </c>
-      <c r="C29">
-        <v>700</v>
-      </c>
-      <c r="D29">
-        <v>700</v>
-      </c>
-      <c r="E29">
-        <v>700</v>
-      </c>
-      <c r="F29">
-        <v>700</v>
+        <v>50</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C30">
-        <v>50</v>
+        <v>700</v>
       </c>
       <c r="D30">
-        <v>50</v>
+        <v>700</v>
       </c>
       <c r="E30">
-        <v>50</v>
+        <v>700</v>
       </c>
       <c r="F30">
-        <v>50</v>
-      </c>
-      <c r="G30" t="s">
-        <v>53</v>
+        <v>700</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C31">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="D31">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="E31">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="F31">
-        <v>55</v>
+        <v>50</v>
+      </c>
+      <c r="G31" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
+        <v>54</v>
+      </c>
+      <c r="C32">
+        <v>55</v>
+      </c>
+      <c r="D32">
+        <v>55</v>
+      </c>
+      <c r="E32">
+        <v>55</v>
+      </c>
+      <c r="F32">
         <v>55</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
         <v>56</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
-        <v>57</v>
-      </c>
-      <c r="B35" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B36" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>61</v>
+        <v>101</v>
       </c>
       <c r="B37" t="s">
-        <v>62</v>
+        <v>102</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>63</v>
+        <v>103</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>64</v>
-      </c>
-      <c r="B39">
-        <v>55</v>
+        <v>104</v>
+      </c>
+      <c r="B39" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>65</v>
+        <v>59</v>
+      </c>
+      <c r="B40" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>66</v>
-      </c>
-      <c r="B41">
-        <v>120</v>
+        <v>61</v>
+      </c>
+      <c r="B41" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>68</v>
+        <v>64</v>
+      </c>
+      <c r="B43">
+        <v>55</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>70</v>
+        <v>66</v>
+      </c>
+      <c r="B45">
+        <v>120</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>72</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>96</v>
+        <v>68</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>74</v>
-      </c>
-      <c r="B49">
-        <v>31.6</v>
+        <v>70</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>75</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>97</v>
+        <v>71</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>76</v>
+        <v>72</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>78</v>
+        <v>74</v>
+      </c>
+      <c r="B53">
+        <v>31.6</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>79</v>
-      </c>
-      <c r="B54">
-        <v>160</v>
+        <v>75</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>83</v>
+        <v>79</v>
+      </c>
+      <c r="B58">
+        <v>160</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
         <v>95</v>
       </c>
     </row>
